--- a/Assets/Excels/Item.xlsx
+++ b/Assets/Excels/Item.xlsx
@@ -1,122 +1,239 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ggj2026\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492BA863-9BE1-425F-90B3-05156A149CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29871" windowHeight="12925"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
+    <sheet name="Attribute" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>属性</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>attribute</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
-    <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>price</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朱砂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金粉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>墨汁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>笔触刚猛，直线向上冲刺</t>
-  </si>
-  <si>
-    <t>笔触锐利，向四周发散。</t>
-  </si>
-  <si>
-    <t>笔触柔顺，向下流淌，且带有惯性（类似惯性漂移）。</t>
-  </si>
-  <si>
-    <t>图标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄铁屑</t>
+  </si>
+  <si>
+    <t>玄铁炼熔后的细屑，凝天地金气，为面具锻铸灵骨，坚而不脆</t>
   </si>
   <si>
     <t>Icon_1</t>
   </si>
   <si>
-    <t>Icon_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>铜铃片</t>
+  </si>
+  <si>
+    <t>古寺铜铃磨下的薄片，藏清越金声，能为面具聚魂，驱散阴翳</t>
+  </si>
+  <si>
+    <t>紫金砂</t>
+  </si>
+  <si>
+    <t>紫金矿脉中结出的细砂，金气醇厚，铸入面具可令灵核凝实，百邪不侵</t>
+  </si>
+  <si>
+    <t>金纹片</t>
+  </si>
+  <si>
+    <t>古器上剥落的鎏金纹路，含岁月金韵，为面具饰骨，增其镇煞之力</t>
+  </si>
+  <si>
+    <t>青竹篾</t>
+  </si>
+  <si>
+    <t>春山嫩竹剖成的细篾，蕴草木生机，为面具塑肌理，柔而有韧</t>
+  </si>
+  <si>
+    <t>柏叶芯</t>
+  </si>
+  <si>
+    <t>古柏新抽的叶芯，藏山林清气，温养面具灵脉，令其气息绵长</t>
+  </si>
+  <si>
+    <t>灵桃木枝</t>
+  </si>
+  <si>
+    <t>东方灵桃枝截成的细段，木气精纯，铸入面具可聚天地生气，滋养灵韵</t>
+  </si>
+  <si>
+    <t>沉香木粉</t>
+  </si>
+  <si>
+    <t>沉香木磨成的细粉，凝草木精华，为面具熏脉，令其灵息醇厚不散</t>
+  </si>
+  <si>
+    <t>清露珠</t>
+  </si>
+  <si>
+    <t>晨朝荷叶上的清露凝珠，蕴天地水气，涤面具尘秽，润其灵韵</t>
+  </si>
+  <si>
+    <t>溪泉石髓</t>
+  </si>
+  <si>
+    <t>溪泉底石中渗出的清髓，藏柔润水意，为面具凝魂，令其灵息澄澈</t>
+  </si>
+  <si>
+    <t>瑶池甘露</t>
+  </si>
+  <si>
+    <t>仙池所凝的甘露，水气清冽醇厚，涤面具浊质，蕴养灵核，令其清透无垢</t>
+  </si>
+  <si>
+    <t>玄冰玉屑</t>
+  </si>
+  <si>
+    <t>极北玄冰玉磨成的细屑，水气化冰，凝而不散，铸入面具可令灵韵坚凝</t>
+  </si>
+  <si>
+    <t>丹枫薪</t>
+  </si>
+  <si>
+    <t>秋山丹枫枝干制成的薪柴，燃之有温火，炼面具灵核，驱散阴寒</t>
+  </si>
+  <si>
+    <t>艾草绒</t>
+  </si>
+  <si>
+    <t>陈年艾草捣成的绒絮，燃之出纯阳火气，为面具驱秽，凝其灵焰</t>
+  </si>
+  <si>
+    <t>凤凰羽灰</t>
+  </si>
+  <si>
+    <t>凤凰羽翼燃后所凝的轻灰，含纯阳真火，炼面具灵骨，焚尽一切阴邪</t>
+  </si>
+  <si>
+    <t>朱砂焰屑</t>
+  </si>
+  <si>
+    <t>朱砂混真火炼出的焰屑，火气相融，铸入面具可令灵焰炽烈，镇煞破障</t>
+  </si>
+  <si>
+    <t>黄黏土</t>
+  </si>
+  <si>
+    <t>中原厚土所出的黄黏土，蕴坤地之气，为面具筑基，固其灵根</t>
+  </si>
+  <si>
+    <t>麦饭石粉</t>
+  </si>
+  <si>
+    <t>古山麦饭石磨成的细粉，藏土之精，承托面具灵韵，令其根基稳固</t>
+  </si>
+  <si>
+    <t>昆仑玉土</t>
+  </si>
+  <si>
+    <t>昆仑山下结出的玉质净土，土气醇厚凝实，为面具铸基，固魂守灵，百扰不侵</t>
+  </si>
+  <si>
+    <t>息壤屑</t>
+  </si>
+  <si>
+    <t>上古息壤所凝的细屑，藏生生不息的土气，承托面具灵核，令其灵韵绵长不散</t>
+  </si>
+  <si>
+    <t>克制</t>
+  </si>
+  <si>
+    <t>被克制</t>
+  </si>
+  <si>
+    <t>restrain</t>
+  </si>
+  <si>
+    <t>restrained</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>土</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -124,20 +241,356 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -145,33 +598,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -220,7 +956,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -255,7 +991,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -429,137 +1165,623 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="17.7166666666667" customWidth="1"/>
+    <col min="3" max="3" width="66.7833333333333" customWidth="1"/>
+    <col min="4" max="4" width="22.575" customWidth="1"/>
+    <col min="5" max="5" width="36.425" customWidth="1"/>
+    <col min="6" max="6" width="12.1416666666667" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>10001</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
+      <c r="B4" t="s">
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
         <v>100</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="1:6">
       <c r="A5" s="1">
         <v>10002</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
+      <c r="B5" t="s">
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2">
-        <v>100</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>10003</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2">
+        <v>200</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>10004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2">
+        <v>250</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>20001</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>20002</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2">
+        <v>150</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>20003</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2">
+        <v>200</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>20004</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2">
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>30001</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>30002</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2">
+        <v>150</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>30003</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>30004</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2">
+        <v>250</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>40001</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="2">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>40002</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2">
+        <v>150</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>40003</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2">
+        <v>200</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>40004</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2">
+        <v>250</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>50001</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="2">
+        <v>100</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>50002</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="2">
+        <v>150</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>50003</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="2">
+        <v>200</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>50004</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="2">
+        <v>250</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="C28" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9.1" defaultRowHeight="14.1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="15.425" customWidth="1"/>
+    <col min="3" max="3" width="26.35" customWidth="1"/>
+    <col min="4" max="4" width="35.4916666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2">
-        <v>150</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excels/Item.xlsx
+++ b/Assets/Excels/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29871" windowHeight="12925"/>
+    <workbookView windowWidth="32065" windowHeight="14160"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -69,12 +69,18 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>玄铁屑</t>
   </si>
   <si>
     <t>玄铁炼熔后的细屑，凝天地金气，为面具锻铸灵骨，坚而不脆</t>
   </si>
   <si>
+    <t>[1,0,0,0,0]</t>
+  </si>
+  <si>
     <t>Icon_1</t>
   </si>
   <si>
@@ -84,6 +90,9 @@
     <t>古寺铜铃磨下的薄片，藏清越金声，能为面具聚魂，驱散阴翳</t>
   </si>
   <si>
+    <t>[2,0,0,0,0]</t>
+  </si>
+  <si>
     <t>紫金砂</t>
   </si>
   <si>
@@ -102,6 +111,9 @@
     <t>春山嫩竹剖成的细篾，蕴草木生机，为面具塑肌理，柔而有韧</t>
   </si>
   <si>
+    <t>[0,1,0,0,0]</t>
+  </si>
+  <si>
     <t>柏叶芯</t>
   </si>
   <si>
@@ -126,6 +138,9 @@
     <t>晨朝荷叶上的清露凝珠，蕴天地水气，涤面具尘秽，润其灵韵</t>
   </si>
   <si>
+    <t>[0,0,1,0,0]</t>
+  </si>
+  <si>
     <t>溪泉石髓</t>
   </si>
   <si>
@@ -150,6 +165,9 @@
     <t>秋山丹枫枝干制成的薪柴，燃之有温火，炼面具灵核，驱散阴寒</t>
   </si>
   <si>
+    <t>[0,0,0,1,0]</t>
+  </si>
+  <si>
     <t>艾草绒</t>
   </si>
   <si>
@@ -172,6 +190,9 @@
   </si>
   <si>
     <t>中原厚土所出的黄黏土，蕴坤地之气，为面具筑基，固其灵根</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,1]</t>
   </si>
   <si>
     <t>麦饭石粉</t>
@@ -229,21 +250,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -699,19 +706,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -720,127 +736,118 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -849,7 +856,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1174,6 +1181,7 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="27.075" customWidth="1"/>
     <col min="2" max="2" width="17.7166666666667" customWidth="1"/>
     <col min="3" max="3" width="66.7833333333333" customWidth="1"/>
     <col min="4" max="4" width="22.575" customWidth="1"/>
@@ -1235,7 +1243,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>12</v>
@@ -1246,19 +1254,19 @@
         <v>10001</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2">
         <v>100</v>
       </c>
-      <c r="E4">
-        <v>1</v>
+      <c r="E4" t="s">
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:6">
@@ -1266,19 +1274,19 @@
         <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
         <v>150</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
+      <c r="E5" t="s">
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1286,19 +1294,19 @@
         <v>10003</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
         <v>200</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
+      <c r="E6" t="s">
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1306,19 +1314,19 @@
         <v>10004</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2">
         <v>250</v>
       </c>
-      <c r="E7" s="2">
-        <v>1</v>
+      <c r="E7" t="s">
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1326,19 +1334,19 @@
         <v>20001</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2">
         <v>100</v>
       </c>
-      <c r="E8" s="2">
-        <v>2</v>
+      <c r="E8" t="s">
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1346,19 +1354,19 @@
         <v>20002</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2">
         <v>150</v>
       </c>
-      <c r="E9" s="2">
-        <v>2</v>
+      <c r="E9" t="s">
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1366,19 +1374,19 @@
         <v>20003</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2">
         <v>200</v>
       </c>
-      <c r="E10">
-        <v>2</v>
+      <c r="E10" t="s">
+        <v>27</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1386,19 +1394,19 @@
         <v>20004</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2">
         <v>250</v>
       </c>
-      <c r="E11">
-        <v>2</v>
+      <c r="E11" t="s">
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1406,19 +1414,19 @@
         <v>30001</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>100</v>
       </c>
-      <c r="E12">
-        <v>3</v>
+      <c r="E12" t="s">
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1426,19 +1434,19 @@
         <v>30002</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2">
         <v>150</v>
       </c>
-      <c r="E13">
-        <v>3</v>
+      <c r="E13" t="s">
+        <v>36</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1446,19 +1454,19 @@
         <v>30003</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2">
         <v>200</v>
       </c>
-      <c r="E14">
-        <v>3</v>
+      <c r="E14" t="s">
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1466,19 +1474,19 @@
         <v>30004</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2">
         <v>250</v>
       </c>
-      <c r="E15">
-        <v>3</v>
+      <c r="E15" t="s">
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1486,19 +1494,19 @@
         <v>40001</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2">
         <v>100</v>
       </c>
-      <c r="E16">
-        <v>4</v>
+      <c r="E16" t="s">
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1506,19 +1514,19 @@
         <v>40002</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2">
         <v>150</v>
       </c>
-      <c r="E17">
-        <v>4</v>
+      <c r="E17" t="s">
+        <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1526,19 +1534,19 @@
         <v>40003</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2">
         <v>200</v>
       </c>
-      <c r="E18">
-        <v>4</v>
+      <c r="E18" t="s">
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1546,19 +1554,19 @@
         <v>40004</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2">
         <v>250</v>
       </c>
-      <c r="E19">
-        <v>4</v>
+      <c r="E19" t="s">
+        <v>45</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1566,19 +1574,19 @@
         <v>50001</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D20" s="2">
         <v>100</v>
       </c>
-      <c r="E20">
-        <v>5</v>
+      <c r="E20" t="s">
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1586,19 +1594,19 @@
         <v>50002</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2">
         <v>150</v>
       </c>
-      <c r="E21">
-        <v>5</v>
+      <c r="E21" t="s">
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1606,19 +1614,19 @@
         <v>50003</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2">
         <v>200</v>
       </c>
-      <c r="E22">
-        <v>5</v>
+      <c r="E22" t="s">
+        <v>54</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1626,19 +1634,19 @@
         <v>50004</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2">
         <v>250</v>
       </c>
-      <c r="E23">
-        <v>5</v>
+      <c r="E23" t="s">
+        <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1676,10 +1684,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1690,10 +1698,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1715,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1729,7 +1737,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1743,7 +1751,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1757,7 +1765,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1771,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>1</v>
